--- a/artfynd/A 5858-2025 artfynd.xlsx
+++ b/artfynd/A 5858-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,38 +675,33 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62127640</v>
+        <v>17317804</v>
       </c>
       <c r="B2" t="n">
-        <v>103427</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221447</v>
+        <v>698</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Sen fältgentiana</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
+          <t>Gentianella campestris var. campestris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513391.7913066337</v>
+        <v>513412</v>
       </c>
       <c r="R2" t="n">
-        <v>6989853.528869865</v>
+        <v>6989839</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,29 +743,24 @@
           <t>Sundsjö</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Z-Brä-0834</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2004-08-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2004-08-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Detalj. 9 ex. inom 2x1 m. Sen Fältgentiana. Mjösjö 1:85, norr om gamla landsvägen, ca 40 m nordnordväst om bostadshuset på Mjösjö 1:85, ca 200 nordnordost om Källmyrbäckens utlopp i Mjösjön, dellokal 3</t>
+          <t>1 ex på ny växtplats, ej återfunnen på de 4 tidigare. Ömsom nyligen kortklippt gräsmatta, ömsom ohävdat med hög vegetation. Timrat hus uppfört på en av de gamla växtplatserna.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,11 +771,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Gräsmatta på gårdsplan. Något sluttande,frisk gräsmark.</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -795,45 +780,44 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo Norell</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Henrik Zetterström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62127641</v>
+        <v>17317824</v>
       </c>
       <c r="B3" t="n">
-        <v>103427</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221447</v>
+        <v>698</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Sen fältgentiana</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
+          <t>Gentianella campestris var. campestris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -843,14 +827,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mjösjö 1:85, Jmt</t>
+          <t>Mjösjö 1:66, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513405.8485433073</v>
+        <v>513531</v>
       </c>
       <c r="R3" t="n">
-        <v>6989860.847644445</v>
+        <v>6989869</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,29 +859,24 @@
           <t>Sundsjö</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Z-Brä-0835</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-08-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-08-17</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Detalj. 1 ex, nyfynd vid NÖ husknuten. Mjösjö 1:85, norr om gamla landsvägen, ca 40 m nordnordväst om bostadshuset på Mjösjö 1:85, ca 200 nordnordost om Källmyrbäckens utlopp i Mjösjön, dellokal 3</t>
+          <t>14 ex inom 9x15 m. Slåtter.  Sen fältgentiana. Följearter: aspskott, åkervädd, daggkåpor, brunört, blodrot, borsttistel, slåtterblomma, späd ögontröst.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,11 +887,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Gräsmatta på gårdsplan.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -922,45 +896,44 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Henrik Zetterström, Elisabet Zetterström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Bo Norell</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>17317824</v>
+        <v>62127640</v>
       </c>
       <c r="B4" t="n">
-        <v>103428</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>106414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>698</v>
+        <v>221447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sen fältgentiana</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gentianella campestris var. campestris</t>
+          <t>Gentianella campestris subsp. campestris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -970,14 +943,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mjösjö 1:66, Jmt</t>
+          <t>Mjösjö 1:85, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513530.7829827761</v>
+        <v>513392</v>
       </c>
       <c r="R4" t="n">
-        <v>6989869.079736313</v>
+        <v>6989854</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,34 +975,19 @@
           <t>Sundsjö</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Z-Brä-0835</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
           <t>2004-08-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2004-08-17</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>14 ex inom 9x15 m. Slåtter.  Sen fältgentiana. Följearter: aspskott, åkervädd, daggkåpor, brunört, blodrot, borsttistel, slåtterblomma, späd ögontröst.</t>
+          <t>Detalj. 9 ex. inom 2x1 m. Sen Fältgentiana. Mjösjö 1:85, norr om gamla landsvägen, ca 40 m nordnordväst om bostadshuset på Mjösjö 1:85, ca 200 nordnordost om Källmyrbäckens utlopp i Mjösjön, dellokal 3</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,6 +998,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Gräsmatta på gårdsplan. Något sluttande,frisk gräsmark.</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1052,11 +1015,231 @@
           <t>Bo Norell</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>62127641</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106414</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221447</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fältgentiana</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mjösjö 1:85, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>513406</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6989861</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2014-09-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2014-09-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Detalj. 1 ex, nyfynd vid NÖ husknuten. Mjösjö 1:85, norr om gamla landsvägen, ca 40 m nordnordväst om bostadshuset på Mjösjö 1:85, ca 200 nordnordost om Källmyrbäckens utlopp i Mjösjön, dellokal 3</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Gräsmatta på gårdsplan.</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Henrik Zetterström, Elisabet Zetterström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>62127643</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106414</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221447</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fältgentiana</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Gentianella campestris subsp. campestris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mjösjö 1:85, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>513412</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6989839</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2004-08-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2004-08-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Detalj. 15 ex. inom 15x6 m. Sen Fältgentiana. Mjösjö 1:85, ca 10 m sydväst om bostadshuset, norr om gamla landsvägen, ca 200 nordnordost om Källmyrbäckens utlopp i Mjösjön</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Slåttermark på gårdstomt. Något, sluttande, torr-frisk mark. Öppet med stenblock.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Bo Norell</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5858-2025 artfynd.xlsx
+++ b/artfynd/A 5858-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17317804</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17317824</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62127640</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62127641</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1240,8 +1265,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62127643</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>